--- a/Problem13_Risk_Adjusted_Profitability_Modeling/reports/financial_impact_reporting_packaging/AMEX_Problem13_Financial_Impact_Workbook.xlsx
+++ b/Problem13_Risk_Adjusted_Profitability_Modeling/reports/financial_impact_reporting_packaging/AMEX_Problem13_Financial_Impact_Workbook.xlsx
@@ -22,10 +22,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="$#,##0;($#,##0);-"/>
+    <numFmt numFmtId="164" formatCode="$#,##0;($#,##0);-"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -76,6 +76,12 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="000B1F3A"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="10">
@@ -138,7 +144,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -146,7 +152,7 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -160,16 +166,23 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -722,7 +735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F13"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -732,6 +745,7 @@
     <col width="3" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -746,6 +760,13 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>Project Portfolio Prepared By Nandagopal R</t>
+        </is>
+      </c>
+    </row>
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -776,7 +797,7 @@
           <t>Net Benefit / Cycle</t>
         </is>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="19">
         <f>'Exposure Impact'!B8</f>
         <v/>
       </c>
@@ -889,7 +910,7 @@
           <t>Exposure Reduction Rate</t>
         </is>
       </c>
-      <c r="B2" s="11" t="n">
+      <c r="B2" s="20" t="n">
         <v>0.25</v>
       </c>
       <c r="C2" s="12" t="inlineStr">
@@ -904,7 +925,7 @@
           <t>Segment Review Cost Usd Per Account</t>
         </is>
       </c>
-      <c r="B3" s="13" t="n">
+      <c r="B3" s="21" t="n">
         <v>18</v>
       </c>
       <c r="C3" s="12" t="inlineStr">
@@ -919,7 +940,7 @@
           <t>Implementation Cost Usd</t>
         </is>
       </c>
-      <c r="B4" s="13" t="n">
+      <c r="B4" s="21" t="n">
         <v>40000</v>
       </c>
       <c r="C4" s="12" t="inlineStr">
@@ -992,7 +1013,7 @@
           <t>Real Total Expected Loss Across Segment (USD)</t>
         </is>
       </c>
-      <c r="B3" s="15" t="n">
+      <c r="B3" s="22" t="n">
         <v>242960310.3195642</v>
       </c>
     </row>
@@ -1002,7 +1023,7 @@
           <t>Real Total Assumption-Scaled Revenue Across Segment (USD)</t>
         </is>
       </c>
-      <c r="B4" s="15" t="n">
+      <c r="B4" s="22" t="n">
         <v>11356144.24554708</v>
       </c>
     </row>
@@ -1022,7 +1043,7 @@
           <t>Gross Exposure-Reduction Benefit / Cycle (USD)</t>
         </is>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="22">
         <f>B3*Assumptions!$B$2</f>
         <v/>
       </c>
@@ -1033,7 +1054,7 @@
           <t>Segment Review Cost / Cycle (USD)</t>
         </is>
       </c>
-      <c r="B7" s="15">
+      <c r="B7" s="22">
         <f>B2*Assumptions!$B$3</f>
         <v/>
       </c>
@@ -1044,7 +1065,7 @@
           <t>Net Benefit / Cycle (USD)</t>
         </is>
       </c>
-      <c r="B8" s="15">
+      <c r="B8" s="22">
         <f>B6-B7</f>
         <v/>
       </c>
@@ -1055,7 +1076,7 @@
           <t>Annual Net Benefit (USD)</t>
         </is>
       </c>
-      <c r="B9" s="15">
+      <c r="B9" s="22">
         <f>B8*Assumptions!$B$5</f>
         <v/>
       </c>
@@ -1142,16 +1163,16 @@
       <c r="C2" t="n">
         <v>0.7213000000000001</v>
       </c>
-      <c r="D2" s="15" t="n">
+      <c r="D2" s="22" t="n">
         <v>76.19</v>
       </c>
-      <c r="E2" s="15" t="n">
+      <c r="E2" s="22" t="n">
         <v>21.37</v>
       </c>
-      <c r="F2" s="15" t="n">
+      <c r="F2" s="22" t="n">
         <v>1622.84</v>
       </c>
-      <c r="G2" s="15" t="n">
+      <c r="G2" s="22" t="n">
         <v>-1601.47</v>
       </c>
       <c r="H2" s="16" t="n">
@@ -1170,16 +1191,16 @@
       <c r="C3" t="n">
         <v>0.1437</v>
       </c>
-      <c r="D3" s="15" t="n">
+      <c r="D3" s="22" t="n">
         <v>67.67</v>
       </c>
-      <c r="E3" s="15" t="n">
+      <c r="E3" s="22" t="n">
         <v>57.53</v>
       </c>
-      <c r="F3" s="15" t="n">
+      <c r="F3" s="22" t="n">
         <v>323.35</v>
       </c>
-      <c r="G3" s="15" t="n">
+      <c r="G3" s="22" t="n">
         <v>-265.82</v>
       </c>
       <c r="H3" s="16" t="n">
@@ -1198,16 +1219,16 @@
       <c r="C4" t="n">
         <v>0.009299999999999999</v>
       </c>
-      <c r="D4" s="15" t="n">
+      <c r="D4" s="22" t="n">
         <v>69.66</v>
       </c>
-      <c r="E4" s="15" t="n">
+      <c r="E4" s="22" t="n">
         <v>68.92</v>
       </c>
-      <c r="F4" s="15" t="n">
+      <c r="F4" s="22" t="n">
         <v>20.92</v>
       </c>
-      <c r="G4" s="15" t="n">
+      <c r="G4" s="22" t="n">
         <v>47.99</v>
       </c>
       <c r="H4" s="16" t="n">
